--- a/SJCE_Benchmark_Graded_Dataset.xlsx
+++ b/SJCE_Benchmark_Graded_Dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65217BC5-F57F-4C87-A10B-87456CAC3197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF77A01-B49D-40B5-B5A0-DD6926039A4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>College_Name</t>
   </si>
@@ -130,13 +130,10 @@
     <t>MIT_Mysore</t>
   </si>
   <si>
-    <t>PESCE_Mysore</t>
-  </si>
-  <si>
     <t>ATME_Mysore</t>
   </si>
   <si>
-    <t>Acharya_Mysore</t>
+    <t>PESCE_Mandya</t>
   </si>
 </sst>
 </file>
@@ -499,11 +496,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="27" customWidth="1"/>
+    <col min="2" max="2" width="7.88671875" customWidth="1"/>
     <col min="3" max="3" width="25.88671875" customWidth="1"/>
-    <col min="4" max="4" width="32" customWidth="1"/>
+    <col min="4" max="4" width="39.77734375" customWidth="1"/>
+    <col min="5" max="5" width="27.5546875" customWidth="1"/>
+    <col min="6" max="6" width="21.88671875" customWidth="1"/>
+    <col min="7" max="7" width="26.88671875" customWidth="1"/>
+    <col min="8" max="8" width="19.5546875" customWidth="1"/>
     <col min="11" max="11" width="12.5546875" customWidth="1"/>
     <col min="12" max="12" width="11.77734375" customWidth="1"/>
     <col min="13" max="13" width="9.21875" customWidth="1"/>
@@ -513,9 +516,9 @@
     <col min="17" max="17" width="23.77734375" customWidth="1"/>
     <col min="18" max="18" width="8.33203125" customWidth="1"/>
     <col min="19" max="19" width="32.77734375" customWidth="1"/>
-    <col min="20" max="20" width="10" customWidth="1"/>
-    <col min="21" max="21" width="13.33203125" customWidth="1"/>
-    <col min="22" max="22" width="12.88671875" customWidth="1"/>
+    <col min="20" max="20" width="26.5546875" customWidth="1"/>
+    <col min="21" max="21" width="29.5546875" customWidth="1"/>
+    <col min="22" max="22" width="28.44140625" customWidth="1"/>
     <col min="23" max="23" width="38.109375" customWidth="1"/>
     <col min="24" max="24" width="37" customWidth="1"/>
     <col min="25" max="25" width="36.5546875" customWidth="1"/>
@@ -1219,7 +1222,7 @@
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C9">
         <v>9.9</v>
@@ -1305,7 +1308,7 @@
     </row>
     <row r="10" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C10">
         <v>9.9</v>
@@ -1387,92 +1390,6 @@
       </c>
       <c r="AC10">
         <v>7.8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11">
-        <v>9.9</v>
-      </c>
-      <c r="D11">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="E11">
-        <v>4</v>
-      </c>
-      <c r="F11">
-        <v>4.2</v>
-      </c>
-      <c r="G11">
-        <v>6.2</v>
-      </c>
-      <c r="H11">
-        <v>6.1</v>
-      </c>
-      <c r="I11">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="J11">
-        <v>3.2</v>
-      </c>
-      <c r="K11">
-        <v>7.2</v>
-      </c>
-      <c r="L11">
-        <v>7.5</v>
-      </c>
-      <c r="M11">
-        <v>8</v>
-      </c>
-      <c r="N11">
-        <v>7</v>
-      </c>
-      <c r="O11">
-        <v>10</v>
-      </c>
-      <c r="P11">
-        <v>7</v>
-      </c>
-      <c r="Q11">
-        <v>7</v>
-      </c>
-      <c r="R11">
-        <v>7.3</v>
-      </c>
-      <c r="S11">
-        <v>10</v>
-      </c>
-      <c r="T11">
-        <v>5.8</v>
-      </c>
-      <c r="U11">
-        <v>3.7</v>
-      </c>
-      <c r="V11">
-        <v>5</v>
-      </c>
-      <c r="W11">
-        <v>6.2</v>
-      </c>
-      <c r="X11">
-        <v>6.5</v>
-      </c>
-      <c r="Y11">
-        <v>7.4</v>
-      </c>
-      <c r="Z11">
-        <v>8</v>
-      </c>
-      <c r="AA11">
-        <v>8.1</v>
-      </c>
-      <c r="AB11">
-        <v>6.2</v>
-      </c>
-      <c r="AC11">
-        <v>7.5</v>
       </c>
     </row>
   </sheetData>
